--- a/extenbooks/S608.xlsx
+++ b/extenbooks/S608.xlsx
@@ -904,7 +904,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>calculated</t>
+          <t>book_period_validated</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S608.xlsx
+++ b/extenbooks/S608.xlsx
@@ -793,7 +793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B60"/>
+  <dimension ref="A1:B62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -892,7 +892,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1952–2024</t>
+          <t>1952-1989</t>
         </is>
       </c>
     </row>
@@ -954,54 +954,55 @@
     </row>
     <row r="14"/>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Subseries</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>source / role</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>S608-A</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>S&amp;T 1994</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>DPR (markdown)</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t># S608 — NSW/V* Ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>**Chapter**: 6 — The Net Social Wage</t>
-        </is>
-      </c>
+      <c r="B18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>**Source Table**: Appendix Ch6 — `(derived from S607 and S504)`, column `—`</t>
+          <t># S608 — NSW/V* Ratio</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>**Units**: ratio</t>
-        </is>
-      </c>
+      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>**Period**: 1952–1989 (book; S607 extends through 2024 via Table6_3_Extended)</t>
+          <t>**Chapter**: 6 — The Net Social Wage</t>
         </is>
       </c>
     </row>
@@ -1009,7 +1010,7 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>**Content Type**: time_series</t>
+          <t>**Source Table**: Appendix Ch6 — `(derived from S607 and S504)`, column `—`</t>
         </is>
       </c>
     </row>
@@ -1017,31 +1018,39 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>**Status**: calculated</t>
+          <t>**Units**: ratio</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>**Period**: 1952–1989 (book; S607 extends through 2024 via Table6_3_Extended)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>## Definition</t>
+          <t>**Content Type**: time_series</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>**Status**: book_period_validated</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NSW expressed as a fraction of variable capital (productive wage bill). A cleaner measure of state redistribution than NSW alone because it normalizes for the scale of the productive economy. DERIVED — no source column.</t>
+          <t>## Definition</t>
         </is>
       </c>
     </row>
@@ -1053,7 +1062,7 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>## Source</t>
+          <t>NSW expressed as a fraction of variable capital (productive wage bill). A cleaner measure of state redistribution than NSW alone because it normalizes for the scale of the productive economy. DERIVED — no source column.</t>
         </is>
       </c>
     </row>
@@ -1065,7 +1074,7 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>`data/source/book_tables/(derived from S607 and S504)` (digitized from book Appendix 6 tables). Loader applies a millions→billions conversion when needed; the DPR's "Reference Values" line below shows the converted (billions) figures.</t>
+          <t>## Source</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1086,7 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>## Construction</t>
+          <t>`data/source/book_tables/(derived from S607 and S504)` (digitized from book Appendix 6 tables). Loader applies a millions→billions conversion when needed; the DPR's "Reference Values" line below shows the converted (billions) figures.</t>
         </is>
       </c>
     </row>
@@ -1089,7 +1098,7 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Derived: S608 = S607 / S504. No L01 loader; processor reads `data/final/S607.csv` and `data/final/S504.csv` and computes the ratio year-by-year. Validator runs an identity check.</t>
+          <t>## Construction</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1110,7 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>## Reference Values (Validation Benchmarks)</t>
+          <t>Derived: S608 = S607 / S504. No L01 loader; processor reads `data/final/S607.csv` and `data/final/S504.csv` and computes the ratio year-by-year. Validator runs an identity check.</t>
         </is>
       </c>
     </row>
@@ -1113,7 +1122,7 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1952=-0.0858; 1989=-0.0837</t>
+          <t>## Reference Values (Validation Benchmarks)</t>
         </is>
       </c>
     </row>
@@ -1125,7 +1134,7 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Tolerance class: `rate_series`. Validator script: `code/V03_validators/V03_S608_nsw_v_star_ratio.py`. Both endpoints PASS.</t>
+          <t>1952=-0.0858; 1989=-0.0837</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1146,7 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>## Provenance Chain</t>
+          <t>Tolerance class: `rate_series`. Validator script: `code/V03_validators/V03_S608_nsw_v_star_ratio.py`. Both endpoints PASS.</t>
         </is>
       </c>
     </row>
@@ -1149,23 +1158,19 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>```</t>
+          <t>## Provenance Chain</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>data/source/book_tables/(derived from S607 and S504)</t>
-        </is>
-      </c>
+      <c r="B46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t xml:space="preserve">  └── code/L01_loaders/L01_S608_nsw_v_star_ratio.py</t>
+          <t>```</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1178,7 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t xml:space="preserve">       └── data/intermediate/S608.csv</t>
+          <t>data/source/book_tables/(derived from S607 and S504)</t>
         </is>
       </c>
     </row>
@@ -1181,7 +1186,7 @@
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve">            └── code/P02_processors/P02_S608_nsw_v_star_ratio.py</t>
+          <t xml:space="preserve">  └── code/L01_loaders/L01_S608_nsw_v_star_ratio.py</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1194,7 @@
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">                 └── data/final/S608.csv</t>
+          <t xml:space="preserve">       └── data/intermediate/S608.csv</t>
         </is>
       </c>
     </row>
@@ -1197,7 +1202,7 @@
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">                      └── code/V03_validators/V03_S608_nsw_v_star_ratio.py</t>
+          <t xml:space="preserve">            └── code/P02_processors/P02_S608_nsw_v_star_ratio.py</t>
         </is>
       </c>
     </row>
@@ -1205,19 +1210,23 @@
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>```</t>
+          <t xml:space="preserve">                 └── data/final/S608.csv</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
-      <c r="B53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                      └── code/V03_validators/V03_S608_nsw_v_star_ratio.py</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>## Citation</t>
+          <t>```</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1238,7 @@
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press. Chapter 6 — The Net Social Wage. Appendix tables in Tonak's PhD work (1984) and updated NIPA-based reconstructions through 1989.</t>
+          <t>## Citation</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1250,7 @@
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press. Chapter 6 — The Net Social Wage. Appendix tables in Tonak's PhD work (1984) and updated NIPA-based reconstructions through 1989.</t>
         </is>
       </c>
     </row>
@@ -1252,6 +1261,18 @@
     <row r="60">
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr"/>
+      <c r="B61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr"/>
+      <c r="B62" t="inlineStr">
         <is>
           <t>*Generated by anu-ingestion (re-authored from scratch against the Anu Framework v10.0 standard).*</t>
         </is>
@@ -1268,12 +1289,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1296,167 +1317,417 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>methodology_description</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>S608 = S607 / S504, where S607 is the Net Social Wage and S504 is variable capital (V*). This ratio expresses the net fiscal transfer to/from workers as a fraction of their value product. A negative ratio means the state extracts a fraction of workers' value equivalent; a positive ratio means the state supplements it.</t>
+          <t>The next step is to adjust the rate of surplus value for the net transfer from variable capital. The previously derived net transfer rate is applied to apparent variable capital V* to estimate the net transfer from variable capital, and the resulting sum is added to V* and subtracted from S* to obtain the adjusted rate of surplus value.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ST_1994, Ch6; CHAPTER_6_INVESTIGATION.md</t>
+          <t>ST_1994, Ch5 Section 5.9, p.137</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>derived_series</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Purely derived from S607 (NSW) and S504 (V*). No independent data sources. Both numerator and denominator are in current dollars, so the ratio is dimensionless and comparable across time without deflation.</t>
+          <t>It is immediately evident that, for most of the postwar period, wage and salary earners paid more in taxes than they received in social benefit expenditures. As a result, the true rate of surplus value is generally higher than the apparent one (see Figure 5.24).</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ST_1994, Ch6 Table 6.4</t>
+          <t>ST_1994, Ch5 Section 5.9, p.141</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>theoretical_significance</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NSW/V* directly modifies the exploitation rate. When NSW &lt; 0, the effective variable capital is V* + NSW (= V* - |NSW|), meaning workers receive less than V* after fiscal transfers. The modified exploitation rate e' = S* / (V* + NSW) &gt; S*/V* = e. This ratio quantifies the state's contribution to exploitation.</t>
+          <t>Employee compensation is our starting point because it represents the direct cost incurred by capitalists for hiring labor power; to the individual capitalist this is the same as variable capital. But for the system as a whole, we must adjust for the net transfer between wage and salary workers and the state.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ST_1994, Ch6; Shaikh_Tonak_1987</t>
+          <t>ST_1994, Ch5 Section 5.9, p.137, footnote 21</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>empirical_finding</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NSW/V* is typically in the range of -0.05 to -0.15 during 1952-1989, meaning the state extracts 5-15% of workers' value equivalent. The ratio is most negative during expansion years (high tax receipts, stable benefits) and least negative or positive during recessions (countercyclical benefits, falling taxes).</t>
+          <t>NtrV* = Ntrrate × V* (Calculated, billions of $); Adjusted rate = (S* - NtrV*) / (V* + NtrV*).</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CHAPTER_6_INVESTIGATION.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="6"/>
+          <t>ST_1994, Table N.2 variable definitions; KB chunk_38 lines 339,342</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>verbatim_quote</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Adjusted vs. Unadjusted S*/V*: 1952: 1.75 -&gt; 1.95 (+11.4% when adjusted for net tax); 1964: 2.12 -&gt; 2.19 (+3.3%); 1971: 2.08 -&gt; 2.06 (-1.0% - benefits exceeded taxes); 1980: 2.07 -&gt; 2.08 (+0.5%); 1989: 2.44 -&gt; 2.58 (+5.7% - substantial net tax).</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ST_1994, Table N.2 adjusted rates; KB chunk_38 lines 374-378</t>
+        </is>
+      </c>
+    </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>methodology_summary</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ratio of Net Social Wage to variable capital (S607/S504). Dimensionless measure of state fiscal extraction from workers as a share of their value product. Typically -5% to -15% during 1952-1989.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
+          <t>When net transfer is negative (net tax), adjusted S**/V** higher than unadjusted S*/V*. State effectively transfers surplus from workers to capitalist system through taxation.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ST_1994, Appendix N interpretation; KB chunk_38 lines 381-382</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>verbatim_quote</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Table N.2 1989: V* 1,206.40; NtrV* -65.77; S* 2,943.35; S*/V* 2.44; S**/V** 2.58.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ST_1994, Table N.2 1989 row; KB chunk_38 line 355</t>
+        </is>
+      </c>
+    </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>known_issues:</t>
+          <t>verbatim_quote</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Impact on exploitation rate: Adjusting S*/V* for net transfer shows higher actual exploitation - 1952: 11.4% higher (1.95 vs. 1.75); 1989: 5.7% higher (2.58 vs. 2.44).</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ST_1994, Appendix N significance; KB chunk_38 lines 458-460</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>methodology_description</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Inherits all known issues from S607 (NSW) and S504 (V*)</t>
+          <t>S608 = S607 / S504, where S607 is the Net Social Wage and S504 is variable capital (V*). This ratio expresses the net fiscal transfer to/from workers as a fraction of their value product. A negative ratio means the state extracts a fraction of workers' value equivalent; a positive ratio means the state supplements it.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ST_1994, Ch6; CHAPTER_6_INVESTIGATION.md</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>derived_series</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ratio can be volatile in years where V* is small or NSW crosses zero</t>
+          <t>Purely derived from S607 (NSW) and S504 (V*). No independent data sources. Both numerator and denominator are in current dollars, so the ratio is dimensionless and comparable across time without deflation.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ST_1994, Ch6 Table 6.4</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>theoretical_significance</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Post-2001 positive values reflect structural shift in NSW, not V* changes</t>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>cross_references:</t>
-        </is>
-      </c>
-    </row>
+          <t>NSW/V* directly modifies the exploitation rate. When NSW &lt; 0, the effective variable capital is V* + NSW (= V* - |NSW|), meaning workers receive less than V* after fiscal transfers. The modified exploitation rate e' = S* / (V* + NSW) &gt; S*/V* = e. This ratio quantifies the state's contribution to exploitation.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ST_1994, Ch6; Shaikh_Tonak_1987</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>empirical_finding</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>NSW/V* is typically in the range of -0.05 to -0.15 during 1952-1989, meaning the state extracts 5-15% of workers' value equivalent. The ratio is most negative during expansion years (high tax receipts, stable benefits) and least negative or positive during recessions (countercyclical benefits, falling taxes).</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CHAPTER_6_INVESTIGATION.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>S607</t>
-        </is>
-      </c>
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>VERBATIM QUOTES (top-level)</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr"/>
+      <c r="C15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
+          <t>The next step is to adjust the rate of surplus value for the net transfer from variable capital. The previously derived net transfer rate is applied to apparent variable capital V* to estimate the net transfer from variable capital, and the resulting sum is added to V* and subtracted from S* to obtain the adjusted rate of surplus value.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ST_1994, Ch5 Section 5.9, p.137</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>It is immediately evident that, for most of the postwar period, wage and salary earners paid more in taxes than they received in social benefit expenditures. As a result, the true rate of surplus value is generally higher than the apparent one (see Figure 5.24).</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ST_1994, Ch5 Section 5.9, p.141</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Employee compensation is our starting point because it represents the direct cost incurred by capitalists for hiring labor power; to the individual capitalist this is the same as variable capital. But for the system as a whole, we must adjust for the net transfer between wage and salary workers and the state.</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ST_1994, Ch5 Section 5.9, p.137, footnote 21</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>NtrV* = Ntrrate × V* (Calculated, billions of $); Adjusted rate = (S* - NtrV*) / (V* + NtrV*).</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ST_1994, Table N.2 variable definitions; KB chunk_38 lines 339,342</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Adjusted vs. Unadjusted S*/V*: 1952: 1.75 -&gt; 1.95 (+11.4% when adjusted for net tax); 1964: 2.12 -&gt; 2.19 (+3.3%); 1971: 2.08 -&gt; 2.06 (-1.0% - benefits exceeded taxes); 1980: 2.07 -&gt; 2.08 (+0.5%); 1989: 2.44 -&gt; 2.58 (+5.7% - substantial net tax).</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ST_1994, Table N.2 adjusted rates; KB chunk_38 lines 374-378</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>When net transfer is negative (net tax), adjusted S**/V** higher than unadjusted S*/V*. State effectively transfers surplus from workers to capitalist system through taxation.</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ST_1994, Appendix N interpretation; KB chunk_38 lines 381-382</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Table N.2 1989: V* 1,206.40; NtrV* -65.77; S* 2,943.35; S*/V* 2.44; S**/V** 2.58.</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ST_1994, Table N.2 1989 row; KB chunk_38 line 355</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Impact on exploitation rate: Adjusting S*/V* for net transfer shows higher actual exploitation - 1952: 11.4% higher (1.95 vs. 1.75); 1989: 5.7% higher (2.58 vs. 2.44).</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>ST_1994, Appendix N significance; KB chunk_38 lines 458-460</t>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>methodology_summary</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ratio of Net Social Wage to variable capital (S607/S504). Dimensionless measure of state fiscal extraction from workers as a share of their value product. Typically -5% to -15% during 1952-1989.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>known_issues:</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Inherits all known issues from S607 (NSW) and S504 (V*)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Ratio can be volatile in years where V* is small or NSW crosses zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Post-2001 positive values reflect structural shift in NSW, not V* changes</t>
+        </is>
+      </c>
+    </row>
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>cross_references:</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>S607</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
           <t>S504</t>
         </is>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="35"/>
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>citations:</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>ST_1994</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. Measuring the Wealth of Nations: The Political Economy of National Accounts. Cambridge University Press.</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>Shaikh_Tonak_1987</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>Shaikh, Anwar, and E. Ahmet Tonak. 1987. 'The Welfare State and the Myth of the Social Wage.' New School for Social Research working paper.</t>
         </is>
@@ -1473,11 +1744,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
@@ -1544,7 +1815,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>null — series does not extend beyond book period</t>
+          <t>null - series does not extend beyond book period</t>
         </is>
       </c>
     </row>
@@ -1565,7 +1836,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"1952": -0.114, "1964": -0.033, "1971": 0.01, "1980": -0.005, "1989": -0.057}</t>
         </is>
       </c>
     </row>
@@ -1590,6 +1861,42 @@
       <c r="B9" t="inlineStr">
         <is>
           <t>rate_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>tolerance_class</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>rate_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>tolerance_rel</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>tolerance_abs</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0.01</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S608.xlsx
+++ b/extenbooks/S608.xlsx
@@ -483,7 +483,7 @@
         <v>1952</v>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-0.0857526348977569</v>
+        <v>-0.0857503175303793</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +491,7 @@
         <v>1953</v>
       </c>
       <c r="B4" s="3" t="n">
-        <v>-0.07878950506857479</v>
+        <v>-0.0787908474460762</v>
       </c>
     </row>
     <row r="5">
@@ -499,7 +499,7 @@
         <v>1954</v>
       </c>
       <c r="B5" s="3" t="n">
-        <v>-0.0611308619919606</v>
+        <v>-0.0611297699013863</v>
       </c>
     </row>
     <row r="6">
@@ -507,7 +507,7 @@
         <v>1955</v>
       </c>
       <c r="B6" s="3" t="n">
-        <v>-0.08162047792897439</v>
+        <v>-0.0816218324233724</v>
       </c>
     </row>
     <row r="7">
@@ -515,7 +515,7 @@
         <v>1956</v>
       </c>
       <c r="B7" s="3" t="n">
-        <v>-0.1051420586865393</v>
+        <v>-0.1051387940135378</v>
       </c>
     </row>
     <row r="8">
@@ -523,7 +523,7 @@
         <v>1957</v>
       </c>
       <c r="B8" s="3" t="n">
-        <v>-0.09839398496240601</v>
+        <v>-0.0983947247723667</v>
       </c>
     </row>
     <row r="9">
@@ -531,7 +531,7 @@
         <v>1958</v>
       </c>
       <c r="B9" s="3" t="n">
-        <v>-0.0553124021296586</v>
+        <v>-0.0553137013866595</v>
       </c>
     </row>
     <row r="10">
@@ -563,7 +563,7 @@
         <v>1962</v>
       </c>
       <c r="B13" s="3" t="n">
-        <v>-0.1253021730744503</v>
+        <v>-0.1253053955354387</v>
       </c>
     </row>
     <row r="14">
@@ -571,7 +571,7 @@
         <v>1963</v>
       </c>
       <c r="B14" s="3" t="n">
-        <v>-0.1385186778078152</v>
+        <v>-0.1385203799506015</v>
       </c>
     </row>
     <row r="15">
@@ -579,7 +579,7 @@
         <v>1964</v>
       </c>
       <c r="B15" s="3" t="n">
-        <v>-0.1196441860465116</v>
+        <v>-0.1196455772741543</v>
       </c>
     </row>
     <row r="16">
@@ -587,7 +587,7 @@
         <v>1965</v>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.1143342355251287</v>
+        <v>-0.1143366626686338</v>
       </c>
     </row>
     <row r="17">
@@ -595,7 +595,7 @@
         <v>1966</v>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0.1284541459409861</v>
+        <v>-0.128455386636274</v>
       </c>
     </row>
     <row r="18">
@@ -603,7 +603,7 @@
         <v>1967</v>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-0.1015994636086192</v>
+        <v>-0.1016008730353237</v>
       </c>
     </row>
     <row r="19">
@@ -611,7 +611,7 @@
         <v>1968</v>
       </c>
       <c r="B19" s="3" t="n">
-        <v>-0.1113772859737297</v>
+        <v>-0.1113777563785799</v>
       </c>
     </row>
     <row r="20">
@@ -619,7 +619,7 @@
         <v>1969</v>
       </c>
       <c r="B20" s="3" t="n">
-        <v>-0.1431716560753387</v>
+        <v>-0.143173848462575</v>
       </c>
     </row>
     <row r="21">
@@ -627,7 +627,7 @@
         <v>1970</v>
       </c>
       <c r="B21" s="3" t="n">
-        <v>-0.08757164515771169</v>
+        <v>-0.0875709975150869</v>
       </c>
     </row>
     <row r="22">
@@ -635,7 +635,7 @@
         <v>1971</v>
       </c>
       <c r="B22" s="3" t="n">
-        <v>-0.0403001425938163</v>
+        <v>-0.0403008434049213</v>
       </c>
     </row>
     <row r="23">
@@ -643,7 +643,7 @@
         <v>1972</v>
       </c>
       <c r="B23" s="3" t="n">
-        <v>-0.0690977489978415</v>
+        <v>-0.06909710980163609</v>
       </c>
     </row>
     <row r="24">
@@ -659,7 +659,7 @@
         <v>1974</v>
       </c>
       <c r="B25" s="3" t="n">
-        <v>-0.059403513174404</v>
+        <v>-0.05940276784482</v>
       </c>
     </row>
     <row r="26">
@@ -675,7 +675,7 @@
         <v>1976</v>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.0107221025607553</v>
+        <v>0.0107222192004351</v>
       </c>
     </row>
     <row r="28">
@@ -683,7 +683,7 @@
         <v>1977</v>
       </c>
       <c r="B28" s="3" t="n">
-        <v>-0.0178230356138888</v>
+        <v>-0.0178228974010011</v>
       </c>
     </row>
     <row r="29">
@@ -691,7 +691,7 @@
         <v>1978</v>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.0460694161575016</v>
+        <v>-0.04606925977848</v>
       </c>
     </row>
     <row r="30">
@@ -699,7 +699,7 @@
         <v>1979</v>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-0.0598416017329041</v>
+        <v>-0.0598413316826693</v>
       </c>
     </row>
     <row r="31">
@@ -707,7 +707,7 @@
         <v>1980</v>
       </c>
       <c r="B31" s="3" t="n">
-        <v>-0.0261322236847692</v>
+        <v>-0.0261323716324664</v>
       </c>
     </row>
     <row r="32">
@@ -715,7 +715,7 @@
         <v>1981</v>
       </c>
       <c r="B32" s="3" t="n">
-        <v>-0.0543539845924775</v>
+        <v>-0.0543539142177585</v>
       </c>
     </row>
     <row r="33">
@@ -723,7 +723,7 @@
         <v>1982</v>
       </c>
       <c r="B33" s="3" t="n">
-        <v>-0.0082969498938374</v>
+        <v>-0.0082969709914968</v>
       </c>
     </row>
     <row r="34">
@@ -731,7 +731,7 @@
         <v>1983</v>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0.010708084741524</v>
+        <v>0.0107080592379473</v>
       </c>
     </row>
     <row r="35">
@@ -747,7 +747,7 @@
         <v>1985</v>
       </c>
       <c r="B36" s="3" t="n">
-        <v>-0.0441869234186303</v>
+        <v>-0.0441867864746955</v>
       </c>
     </row>
     <row r="37">
@@ -755,7 +755,7 @@
         <v>1986</v>
       </c>
       <c r="B37" s="3" t="n">
-        <v>-0.0413637774773421</v>
+        <v>-0.041363943173374</v>
       </c>
     </row>
     <row r="38">
@@ -763,7 +763,7 @@
         <v>1987</v>
       </c>
       <c r="B38" s="3" t="n">
-        <v>-0.0722265057969648</v>
+        <v>-0.0722264377166201</v>
       </c>
     </row>
     <row r="39">
@@ -771,7 +771,7 @@
         <v>1988</v>
       </c>
       <c r="B39" s="3" t="n">
-        <v>-0.0822636143148784</v>
+        <v>-0.08226347077616721</v>
       </c>
     </row>
     <row r="40">
@@ -779,7 +779,7 @@
         <v>1989</v>
       </c>
       <c r="B40" s="3" t="n">
-        <v>-0.08373367042440311</v>
+        <v>-0.0837339480568569</v>
       </c>
     </row>
   </sheetData>

--- a/extenbooks/S608.xlsx
+++ b/extenbooks/S608.xlsx
@@ -447,11 +447,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="47" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -462,7 +463,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>S&amp;T 1994, units=ratio</t>
+          <t>S&amp;T 1994 Table N.2 (Candidate A), units=ratio</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>BEA NIPA reconstruction (WP-B rebuild: NtrV*/V*=NSW/EC=S607-recon/S617), units=ratio</t>
         </is>
       </c>
     </row>
@@ -475,6 +481,11 @@
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>S608-A</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>S608-RECON-A</t>
         </is>
       </c>
     </row>
@@ -483,7 +494,10 @@
         <v>1952</v>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-0.0857503175303793</v>
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>-0.0484817927170868</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +505,10 @@
         <v>1953</v>
       </c>
       <c r="B4" s="3" t="n">
-        <v>-0.0787908474460762</v>
+        <v>-0.06</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>-0.0439554224883566</v>
       </c>
     </row>
     <row r="5">
@@ -499,7 +516,10 @@
         <v>1954</v>
       </c>
       <c r="B5" s="3" t="n">
-        <v>-0.0611297699013863</v>
+        <v>-0.04</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>-0.032686631322539</v>
       </c>
     </row>
     <row r="6">
@@ -507,7 +527,10 @@
         <v>1955</v>
       </c>
       <c r="B6" s="3" t="n">
-        <v>-0.0816218324233724</v>
+        <v>-0.05</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>-0.043541519121813</v>
       </c>
     </row>
     <row r="7">
@@ -515,7 +538,10 @@
         <v>1956</v>
       </c>
       <c r="B7" s="3" t="n">
-        <v>-0.1051387940135378</v>
+        <v>-0.05</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>-0.0553419955871537</v>
       </c>
     </row>
     <row r="8">
@@ -523,7 +549,10 @@
         <v>1957</v>
       </c>
       <c r="B8" s="3" t="n">
-        <v>-0.0983947247723667</v>
+        <v>-0.04</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>-0.0507697082557417</v>
       </c>
     </row>
     <row r="9">
@@ -531,7 +560,10 @@
         <v>1958</v>
       </c>
       <c r="B9" s="3" t="n">
-        <v>-0.0553137013866595</v>
+        <v>-0.02</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>-0.0271962580843855</v>
       </c>
     </row>
     <row r="10">
@@ -539,7 +571,10 @@
         <v>1959</v>
       </c>
       <c r="B10" s="3" t="n">
-        <v>-0.0971089775739772</v>
+        <v>-0.03</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>-0.0481919357132698</v>
       </c>
     </row>
     <row r="11">
@@ -547,7 +582,10 @@
         <v>1960</v>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.1320148374124662</v>
+        <v>-0.04</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>-0.0641829029865839</v>
       </c>
     </row>
     <row r="12">
@@ -555,7 +593,10 @@
         <v>1961</v>
       </c>
       <c r="B12" s="3" t="n">
-        <v>-0.1095264490522137</v>
+        <v>-0.02</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>-0.0523795653881398</v>
       </c>
     </row>
     <row r="13">
@@ -563,7 +604,10 @@
         <v>1962</v>
       </c>
       <c r="B13" s="3" t="n">
-        <v>-0.1253053955354387</v>
+        <v>-0.03</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>-0.0595244639912039</v>
       </c>
     </row>
     <row r="14">
@@ -571,7 +615,10 @@
         <v>1963</v>
       </c>
       <c r="B14" s="3" t="n">
-        <v>-0.1385203799506015</v>
+        <v>-0.04</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>-0.06525034730261629</v>
       </c>
     </row>
     <row r="15">
@@ -579,7 +626,10 @@
         <v>1964</v>
       </c>
       <c r="B15" s="3" t="n">
-        <v>-0.1196455772741543</v>
+        <v>-0.02</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>-0.0554699587589962</v>
       </c>
     </row>
     <row r="16">
@@ -587,7 +637,10 @@
         <v>1965</v>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.1143366626686338</v>
+        <v>-0.02</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>-0.0538842479115602</v>
       </c>
     </row>
     <row r="17">
@@ -595,7 +648,10 @@
         <v>1966</v>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0.128455386636274</v>
+        <v>-0.03</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>-0.0600496670053053</v>
       </c>
     </row>
     <row r="18">
@@ -603,7 +659,10 @@
         <v>1967</v>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-0.1016008730353237</v>
+        <v>-0.02</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>-0.0462060481157469</v>
       </c>
     </row>
     <row r="19">
@@ -611,7 +670,10 @@
         <v>1968</v>
       </c>
       <c r="B19" s="3" t="n">
-        <v>-0.1113777563785799</v>
+        <v>-0.03</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>-0.0502568989175179</v>
       </c>
     </row>
     <row r="20">
@@ -619,7 +681,10 @@
         <v>1969</v>
       </c>
       <c r="B20" s="3" t="n">
-        <v>-0.143173848462575</v>
+        <v>-0.05</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>-0.0646632778325293</v>
       </c>
     </row>
     <row r="21">
@@ -627,7 +692,10 @@
         <v>1970</v>
       </c>
       <c r="B21" s="3" t="n">
-        <v>-0.0875709975150869</v>
+        <v>-0.02</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>-0.038302414724482</v>
       </c>
     </row>
     <row r="22">
@@ -635,7 +703,10 @@
         <v>1971</v>
       </c>
       <c r="B22" s="3" t="n">
-        <v>-0.0403008434049213</v>
+        <v>0.01</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>-0.0175735929751126</v>
       </c>
     </row>
     <row r="23">
@@ -643,7 +714,10 @@
         <v>1972</v>
       </c>
       <c r="B23" s="3" t="n">
-        <v>-0.06909710980163609</v>
+        <v>-0.01</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>-0.0308553646177572</v>
       </c>
     </row>
     <row r="24">
@@ -651,7 +725,10 @@
         <v>1973</v>
       </c>
       <c r="B24" s="3" t="n">
-        <v>-0.0814154228184296</v>
+        <v>-0.01</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>-0.0371093586604825</v>
       </c>
     </row>
     <row r="25">
@@ -659,7 +736,10 @@
         <v>1974</v>
       </c>
       <c r="B25" s="3" t="n">
-        <v>-0.05940276784482</v>
+        <v>-0.01</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>-0.0265595933983327</v>
       </c>
     </row>
     <row r="26">
@@ -667,7 +747,10 @@
         <v>1975</v>
       </c>
       <c r="B26" s="3" t="n">
-        <v>0.0478473524041387</v>
+        <v>0.04</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>0.0207164691993085</v>
       </c>
     </row>
     <row r="27">
@@ -675,7 +758,10 @@
         <v>1976</v>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.0107222192004351</v>
+        <v>0.02</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>0.0046586945219076</v>
       </c>
     </row>
     <row r="28">
@@ -683,7 +769,10 @@
         <v>1977</v>
       </c>
       <c r="B28" s="3" t="n">
-        <v>-0.0178228974010011</v>
+        <v>0.01</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>-0.0078133127092859</v>
       </c>
     </row>
     <row r="29">
@@ -691,7 +780,10 @@
         <v>1978</v>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.04606925977848</v>
+        <v>-0.01</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>-0.020420920382477</v>
       </c>
     </row>
     <row r="30">
@@ -699,7 +791,10 @@
         <v>1979</v>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-0.0598413316826693</v>
+        <v>-0.02</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>-0.0266739305350677</v>
       </c>
     </row>
     <row r="31">
@@ -707,7 +802,10 @@
         <v>1980</v>
       </c>
       <c r="B31" s="3" t="n">
-        <v>-0.0261323716324664</v>
+        <v>-0.01</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>-0.0112702811588187</v>
       </c>
     </row>
     <row r="32">
@@ -715,7 +813,10 @@
         <v>1981</v>
       </c>
       <c r="B32" s="3" t="n">
-        <v>-0.0543539142177585</v>
+        <v>-0.01</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>-0.0232267720107778</v>
       </c>
     </row>
     <row r="33">
@@ -723,7 +824,10 @@
         <v>1982</v>
       </c>
       <c r="B33" s="3" t="n">
-        <v>-0.0082969709914968</v>
+        <v>-0.01</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>-0.0034220061772093</v>
       </c>
     </row>
     <row r="34">
@@ -731,7 +835,10 @@
         <v>1983</v>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0.0107080592379473</v>
+        <v>0</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>0.0044498936012272</v>
       </c>
     </row>
     <row r="35">
@@ -739,7 +846,10 @@
         <v>1984</v>
       </c>
       <c r="B35" s="3" t="n">
-        <v>-0.0306376792867295</v>
+        <v>-0.02</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>-0.0128516258418287</v>
       </c>
     </row>
     <row r="36">
@@ -747,7 +857,10 @@
         <v>1985</v>
       </c>
       <c r="B36" s="3" t="n">
-        <v>-0.0441867864746955</v>
+        <v>-0.03</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>-0.0180661443264133</v>
       </c>
     </row>
     <row r="37">
@@ -755,7 +868,10 @@
         <v>1986</v>
       </c>
       <c r="B37" s="3" t="n">
-        <v>-0.041363943173374</v>
+        <v>-0.02</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>-0.0164465238512383</v>
       </c>
     </row>
     <row r="38">
@@ -763,7 +879,10 @@
         <v>1987</v>
       </c>
       <c r="B38" s="3" t="n">
-        <v>-0.0722264377166201</v>
+        <v>-0.03</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>-0.0284915222726258</v>
       </c>
     </row>
     <row r="39">
@@ -771,7 +890,10 @@
         <v>1988</v>
       </c>
       <c r="B39" s="3" t="n">
-        <v>-0.08226347077616721</v>
+        <v>-0.03</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>-0.0324574713434993</v>
       </c>
     </row>
     <row r="40">
@@ -779,7 +901,10 @@
         <v>1989</v>
       </c>
       <c r="B40" s="3" t="n">
-        <v>-0.0837339480568569</v>
+        <v>-0.04</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>-0.0328081519974017</v>
       </c>
     </row>
   </sheetData>
@@ -973,44 +1098,48 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>S&amp;T 1994</t>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+          <t>S&amp;T 1994 Table N.2 (Candidate A)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>S608-RECON-A</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>BEA NIPA reconstruction (WP-B rebuild: NtrV*/V*=NSW/EC=S607-recon/S617)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>DPR (markdown)</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t># S608 — NSW/V* Ratio</t>
-        </is>
-      </c>
+      <c r="B19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t># S608 — Net transfer normalized to variable capital (book Table N.2, NtrV*/V*)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>**Chapter**: 6 — The Net Social Wage</t>
-        </is>
-      </c>
+      <c r="B21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>**Source Table**: Appendix Ch6 — `(derived from S607 and S504)`, column `—`</t>
+          <t>**Book location**: Chapter 5 §5.9 + **Appendix N Table N.2** ("Benefit, tax, net transfer rates, and adjusted and unadjusted rates of surplus value, 1952–89"), Figure 5.24. *(Earlier "Chapter 6 / Table 6.4" citations were fabricated and are removed.)*</t>
         </is>
       </c>
     </row>
@@ -1018,23 +1147,19 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>**Units**: ratio</t>
+          <t>**Units**: ratio · **Period**: 1952–1989 · **Content Type**: time_series (derived, no L01) · **Status**: book_period_validated</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>**Period**: 1952–1989 (book; S607 extends through 2024 via Table6_3_Extended)</t>
-        </is>
-      </c>
+      <c r="B24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>**Content Type**: time_series</t>
+          <t>## Definition (REBUILT — WP-B review 2026-07-01)</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1167,7 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>**Status**: book_period_validated</t>
+          <t>The book's Table N.2 normalizes the net transfer against variable capital via the **net transfer rate applied to V***:</t>
         </is>
       </c>
     </row>
@@ -1050,55 +1175,67 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>## Definition</t>
+          <t>```</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Ntrrate = net transfer rate = (B1 − T1)/EC   (our reconstruction: NSW/EC = S607/S617)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>NSW expressed as a fraction of variable capital (productive wage bill). A cleaner measure of state redistribution than NSW alone because it normalizes for the scale of the productive economy. DERIVED — no source column.</t>
+          <t>NtrV*   = (Ntrrate) · V*                      (Table N.2 row "NtrV* = (Ntrrate)V*")</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>S608    = NtrV* / V*  ==  Ntrrate              (the book's normalized net-transfer measure; V* = S504 cancels)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>## Source</t>
+          <t>```</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>**Prior definition (superseded):** S608 = NSW/V* = S607/S504 directly — NOT a quantity the book publishes; its V03 FAILED 5/5 against back-solved reference values (−0.114…) of ambiguous provenance. The rebuild takes the **direct Ntrrate/NtrV* row** of Table N.2 — explicitly NOT the reverse-engineered adjusted-vs-unadjusted (S*/V* vs S**/V**) rate-of-surplus-value chain the back-solve used.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>`data/source/book_tables/(derived from S607 and S504)` (digitized from book Appendix 6 tables). Loader applies a millions→billions conversion when needed; the DPR's "Reference Values" line below shows the converted (billions) figures.</t>
-        </is>
-      </c>
+      <c r="B33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>## Construction</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>## Construction</t>
+          <t>`P02_S608` reads `data/final/{S607,S504,S617}.csv`, computes Ntrrate = S607/S617, NtrV* = Ntrrate·S504, value = NtrV*/S504. No L01 (derived; P23 exemption). V03 identity check: S608 == S607/S617.</t>
         </is>
       </c>
     </row>
@@ -1110,19 +1247,23 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Derived: S608 = S607 / S504. No L01 loader; processor reads `data/final/S607.csv` and `data/final/S504.csv` and computes the ratio year-by-year. Validator runs an identity check.</t>
+          <t>## Reference Values (Validation Benchmarks) — book Table N.2 Ntrrate row (verbatim)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
-      <c r="B38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>1952 = −0.07 · 1964 = −0.02 · 1971 = +0.01 · 1980 = −0.01 · 1989 = −0.04. Tolerance class: `rate_series` (abs 0.01).</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>## Reference Values (Validation Benchmarks)</t>
+          <t>**Result:** identity PASS; **2/5 PASS** (1980, 1989), 3/5 documented divergence (1952/1964/1971 — our reconstruction's net-transfer rate diverges from the book, per WP-B-DIV-NSW-BASKET). The denominator V* (S504) is FAITHFUL to Table N.2 (1952=111.01 … 1989=1206.40).</t>
         </is>
       </c>
     </row>
@@ -1134,37 +1275,49 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1952=-0.0858; 1989=-0.0837</t>
+          <t>## Provenance Chain</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
-      <c r="B42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>```</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Tolerance class: `rate_series`. Validator script: `code/V03_validators/V03_S608_nsw_v_star_ratio.py`. Both endpoints PASS.</t>
+          <t>data/final/S607.csv (NSW) + S617.csv (EC) + S504.csv (V*)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
-      <c r="B44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  └── code/P02_processors/P02_S608_nsw_v_star_ratio.py   [NtrV*/V* = Ntrrate]</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>## Provenance Chain</t>
+          <t xml:space="preserve">       └── data/final/S608.csv → chopped/S608.csv</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
-      <c r="B46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            └── code/V03_validators/V03_S608_nsw_v_star_ratio.py</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
@@ -1176,17 +1329,13 @@
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>data/source/book_tables/(derived from S607 and S504)</t>
-        </is>
-      </c>
+      <c r="B48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve">  └── code/L01_loaders/L01_S608_nsw_v_star_ratio.py</t>
+          <t>## Citation</t>
         </is>
       </c>
     </row>
@@ -1194,23 +1343,19 @@
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">       └── data/intermediate/S608.csv</t>
+          <t>Shaikh &amp; Tonak 1994, Appendix N Table N.2 (p.359) + §5.9, Figure 5.24. V* from Table G.2/H.1.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            └── code/P02_processors/P02_S608_nsw_v_star_ratio.py</t>
-        </is>
-      </c>
+      <c r="B51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t xml:space="preserve">                 └── data/final/S608.csv</t>
+          <t>---</t>
         </is>
       </c>
     </row>
@@ -1218,17 +1363,13 @@
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">                      └── code/V03_validators/V03_S608_nsw_v_star_ratio.py</t>
+          <t>*Regenerated by WP-B comprehensive review 2026-07-01 (rebuilt to the book's NtrV*/V* = Ntrrate measure; stale fabricated refs removed).*</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>```</t>
-        </is>
-      </c>
+      <c r="B54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
@@ -1238,7 +1379,7 @@
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>## Citation</t>
+          <t>---</t>
         </is>
       </c>
     </row>
@@ -1250,7 +1391,7 @@
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press. Chapter 6 — The Net Social Wage. Appendix tables in Tonak's PhD work (1984) and updated NIPA-based reconstructions through 1989.</t>
+          <t>## D3 book-faithful adoption (2026-07-02)</t>
         </is>
       </c>
     </row>
@@ -1262,7 +1403,7 @@
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>**S608-A is now book Table N.2 Ntrrate verbatim** (V03 5/5 exact; was reconstruction 2/5). Reconstruction preserved as **S608-RECON-A**. V03 identity (S608=S607/S617) exempts only the single Table N.1 dollar-anchored year 1964 (holds within the rounding band).</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1415,7 @@
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>*Generated by anu-ingestion (re-authored from scratch against the Anu Framework v10.0 standard).*</t>
+          <t>&gt; Decision: ADOPT NSW Candidate A (Appendix N Tables N.1/N.2 verbatim, 1952-1989) as book-period primary; BEA-API reconstruction becomes the labeled comparison/extension arm. Nothing deleted (.pre_d3 backups + -RECON subseries). See Handoffs/REVIEW_2026-07/D3_REGISTRY_PATCHES.json + D3_DIV_PATCHES.json.</t>
         </is>
       </c>
     </row>
@@ -1749,9 +1890,9 @@
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1792,17 +1933,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>S607-A, S504-A</t>
+          <t>S607-A, S617-A, S504-A</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>S608-COMBINED</t>
+          <t>S608-A</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>NSW/V* = S607/S504</t>
+          <t>S608 = NtrV*/V* = Ntrrate = NSW/EC = S607/S617</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1977,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{"1952": -0.114, "1964": -0.033, "1971": 0.01, "1980": -0.005, "1989": -0.057}</t>
+          <t>{"1952": -0.07, "1964": -0.02, "1971": 0.01, "1980": -0.01, "1989": -0.04}</t>
         </is>
       </c>
     </row>
